--- a/app/reporting/cdm_reports/02_logistics_segment/02_logistics_segment_V1_Initial_Fidelity_Report.xlsx
+++ b/app/reporting/cdm_reports/02_logistics_segment/02_logistics_segment_V1_Initial_Fidelity_Report.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DASHBOARD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="FINDINGS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ENTITY_MATRIX" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="RELATIONSHIPS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="CATEGORY_ANALYSIS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DESCRIPTION" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="CONFIG" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="02_logistics_segment" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINDINGS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENTITY_MATRIX" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RELATIONSHIPS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATEGORY_ANALYSIS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DESCRIPTION" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_logistics_segment" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SUMMARY'!$A$2:$AG$3</definedName>
@@ -323,13 +323,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -348,7 +348,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -388,8 +388,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -412,7 +412,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -427,9 +427,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -768,7 +768,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SAP PD (PowerDesigner CDM) → erwin  |  Conceptual Model Validation Report   |   generated 2026-09-04 19:47</t>
+          <t>SAP PD (PowerDesigner CDM) → erwin  |  Conceptual Model Validation Report   |   generated 2026-09-05 21:17</t>
         </is>
       </c>
     </row>

--- a/app/reporting/cdm_reports/02_logistics_segment/02_logistics_segment_V1_Initial_Fidelity_Report.xlsx
+++ b/app/reporting/cdm_reports/02_logistics_segment/02_logistics_segment_V1_Initial_Fidelity_Report.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINDINGS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENTITY_MATRIX" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RELATIONSHIPS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATEGORY_ANALYSIS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DESCRIPTION" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_logistics_segment" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DASHBOARD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="FINDINGS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ENTITY_MATRIX" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="RELATIONSHIPS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CATEGORY_ANALYSIS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DESCRIPTION" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CONFIG" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="02_logistics_segment" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SUMMARY'!$A$2:$AG$3</definedName>
@@ -323,13 +323,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -348,7 +348,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -388,8 +388,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -412,7 +412,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -427,9 +427,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -768,7 +768,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SAP PD (PowerDesigner CDM) → erwin  |  Conceptual Model Validation Report   |   generated 2026-09-05 21:17</t>
+          <t>SAP PD (PowerDesigner CDM) → erwin  |  Conceptual Model Validation Report   |   generated 2026-09-05 20:24</t>
         </is>
       </c>
     </row>
